--- a/Sensitivity_rho_Plane.xlsx
+++ b/Sensitivity_rho_Plane.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD0D70E1-6832-4AB6-8FEA-6D4D0CD6339C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29D09162-790B-49D0-B63D-EAB191FBD607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A38E806E-AE9A-4578-B5B1-0C94CEE581C5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D6E5CE80-F249-4AC4-A100-22C75DC023B9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -418,7 +421,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A76DCABA-B5EF-4526-B116-C8A5A846DCAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F86D39-08FA-43E6-975E-ECE9A7508F47}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -509,7 +512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4208A685-DBFE-4748-8386-879DF32699D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B85DC583-C538-4513-BD6E-797E9C166AB4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -518,7 +521,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8434EF01-D1A6-4F70-83E2-2CDBFE5B7AB8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAAE2CD3-37DB-4FCC-8EC4-11CB4EF0DB02}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
